--- a/server/templates/RepairTemplate.xlsx
+++ b/server/templates/RepairTemplate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\ctmq\server\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21714DA0-7D7C-498B-B241-8FA79437C6EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F257D876-8842-483D-8144-F3CE2A17AC11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{5D67107F-0276-4389-B413-20A1926A4355}"/>
+    <workbookView xWindow="5070" yWindow="690" windowWidth="23730" windowHeight="10530" xr2:uid="{5D67107F-0276-4389-B413-20A1926A4355}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -157,6 +157,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -492,24 +502,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76286F2A-184B-47FC-A7C3-3249AA667548}">
   <dimension ref="A1:R19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" customWidth="1"/>
-    <col min="3" max="3" width="18.36328125" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.26953125" customWidth="1"/>
-    <col min="6" max="6" width="18.36328125" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="12" max="12" width="14.453125" customWidth="1"/>
-    <col min="13" max="13" width="10.81640625" customWidth="1"/>
-    <col min="14" max="14" width="15.26953125" customWidth="1"/>
-    <col min="15" max="15" width="21.90625" customWidth="1"/>
-    <col min="16" max="16" width="20.36328125" customWidth="1"/>
-    <col min="17" max="17" width="26.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="7"/>
+    <col min="10" max="10" width="14" style="7" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="10"/>
+    <col min="12" max="12" width="14.42578125" style="7" customWidth="1"/>
+    <col min="13" max="13" width="10.85546875" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" customWidth="1"/>
+    <col min="16" max="16" width="20.42578125" customWidth="1"/>
+    <col min="17" max="17" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -531,19 +543,19 @@
       <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="4" t="s">
@@ -563,7 +575,7 @@
       </c>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -571,18 +583,18 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="6"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -590,18 +602,18 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="6"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -609,18 +621,18 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="6"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -628,18 +640,18 @@
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="6"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -647,18 +659,18 @@
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="6"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -666,18 +678,18 @@
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="6"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -685,18 +697,18 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="6"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -704,18 +716,18 @@
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="6"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -723,18 +735,18 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="6"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -742,18 +754,18 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="6"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -761,18 +773,18 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="6"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -780,18 +792,18 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="6"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -799,18 +811,18 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="6"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -818,18 +830,18 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="6"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -837,18 +849,18 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="6"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -856,18 +868,18 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -875,18 +887,18 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -894,11 +906,11 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="6"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
